--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BIELE ISB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BIELE ISB.xlsx
@@ -565,67 +565,67 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6911</v>
+        <v>12.6237</v>
       </c>
       <c r="E2" t="n">
-        <v>17.9663</v>
+        <v>18.3843</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.2752</v>
+        <v>-5.7606</v>
       </c>
       <c r="G2" t="n">
-        <v>7.396</v>
+        <v>7.4195</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7385</v>
+        <v>6.8345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6576</v>
+        <v>0.5851</v>
       </c>
       <c r="J2" t="n">
-        <v>11.1245</v>
+        <v>11.3765</v>
       </c>
       <c r="K2" t="n">
-        <v>10.5316</v>
+        <v>10.7802</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.7282</v>
+        <v>-3.9569</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.7931</v>
+        <v>-3.9456</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06490000000000001</v>
+        <v>-0.01120000000000013</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4097000000000001</v>
+        <v>-0.4048999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6.3502</v>
+        <v>-6.2761</v>
       </c>
       <c r="R2" t="n">
-        <v>5.9405</v>
+        <v>5.8712</v>
       </c>
       <c r="S2" t="n">
-        <v>10.9121</v>
+        <v>10.8187</v>
       </c>
       <c r="T2" t="n">
-        <v>8.546200000000001</v>
+        <v>8.5517</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3658</v>
+        <v>2.267</v>
       </c>
       <c r="V2" t="n">
-        <v>-5.2074</v>
+        <v>-5.2097</v>
       </c>
       <c r="W2" t="n">
-        <v>4.646000000000001</v>
+        <v>4.732</v>
       </c>
       <c r="X2" t="n">
-        <v>-9.853400000000001</v>
+        <v>-9.941700000000001</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.728399999999999</v>
+        <v>2.696200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6037000000000003</v>
+        <v>1.007699999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1247</v>
+        <v>1.6884</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.3344</v>
+        <v>-4.3418</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5247</v>
+        <v>-1.5223</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.8098</v>
+        <v>-2.819599999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1713</v>
+        <v>3.3784</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1883</v>
+        <v>3.3332</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.01690000000000003</v>
+        <v>0.04519999999999991</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.5057</v>
+        <v>-7.7204</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.712899999999999</v>
+        <v>-4.8555</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.7927</v>
+        <v>-2.865</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.6873</v>
+        <v>-3.6441</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.4472</v>
+        <v>-10.3251</v>
       </c>
       <c r="R3" t="n">
-        <v>6.7599</v>
+        <v>6.681</v>
       </c>
       <c r="S3" t="n">
-        <v>8.182399999999999</v>
+        <v>8.1282</v>
       </c>
       <c r="T3" t="n">
-        <v>4.6862</v>
+        <v>4.7277</v>
       </c>
       <c r="U3" t="n">
-        <v>3.4962</v>
+        <v>3.4005</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5676</v>
+        <v>2.5539</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1936</v>
+        <v>3.2264</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.626</v>
+        <v>-0.6725</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.586499999999999</v>
+        <v>1.854100000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5312</v>
+        <v>4.194</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9444</v>
+        <v>-2.3399</v>
       </c>
       <c r="G4" t="n">
-        <v>3.916300000000001</v>
+        <v>4.1402</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5442</v>
+        <v>-1.5419</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4604</v>
+        <v>5.6823</v>
       </c>
       <c r="J4" t="n">
-        <v>10.0055</v>
+        <v>10.4588</v>
       </c>
       <c r="K4" t="n">
-        <v>2.472</v>
+        <v>2.6215</v>
       </c>
       <c r="L4" t="n">
-        <v>7.533600000000001</v>
+        <v>7.8374</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.0893</v>
+        <v>-6.3185</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.0161</v>
+        <v>-4.1633</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0731</v>
+        <v>-2.1551</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.5551</v>
+        <v>-6.478499999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>5.9405</v>
+        <v>5.8712</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5486</v>
+        <v>-1.5097</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.0681</v>
+        <v>-1.9803</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5195</v>
+        <v>0.4707000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1665000000000005</v>
+        <v>-0.1692</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1488</v>
+        <v>2.194</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3154</v>
+        <v>-2.3632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2485</v>
+        <v>1.2067</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7196</v>
+        <v>2.1709</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4709</v>
+        <v>-0.9642000000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3478999999999999</v>
+        <v>-1.21</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1597</v>
+        <v>0.7278999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5076000000000001</v>
+        <v>-1.9379</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1537</v>
+        <v>6.1175</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2949</v>
+        <v>6.4716</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8587999999999999</v>
+        <v>-0.3541000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.805800000000001</v>
+        <v>-7.327599999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.4546</v>
+        <v>-5.7438</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3513</v>
+        <v>-1.5838</v>
       </c>
       <c r="P5" t="n">
-        <v>3.0726</v>
+        <v>2.4295</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0484</v>
+        <v>-5.4662</v>
       </c>
       <c r="R5" t="n">
-        <v>5.1212</v>
+        <v>7.8956</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2376</v>
+        <v>0.1995999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3987000000000001</v>
+        <v>-1.8645</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6363</v>
+        <v>2.0641</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4096</v>
+        <v>-0.2122999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>2.013</v>
+        <v>3.3841</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.4227</v>
+        <v>-3.5964</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.123799999999999</v>
+        <v>1.1135</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6157</v>
+        <v>2.8862</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4921</v>
+        <v>-1.7726</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.292</v>
+        <v>0.2727999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6589</v>
+        <v>-0.2147000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9509</v>
+        <v>0.4874999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7781</v>
+        <v>3.2313</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2362</v>
+        <v>2.3495</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4580999999999997</v>
+        <v>0.8819</v>
       </c>
       <c r="M6" t="n">
-        <v>-7.0701</v>
+        <v>-2.9584</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.5773</v>
+        <v>-2.5642</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4928</v>
+        <v>-0.3942999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4581</v>
+        <v>3.0369</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.530900000000001</v>
+        <v>-2.0246</v>
       </c>
       <c r="R6" t="n">
-        <v>7.989100000000001</v>
+        <v>5.061299999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1819000000000001</v>
+        <v>0.2345</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.9608</v>
+        <v>-0.357</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1427</v>
+        <v>0.5912999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2242000000000002</v>
+        <v>-2.4306</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3295</v>
+        <v>2.0362</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.5537</v>
+        <v>-4.4668</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7814000000000001</v>
+        <v>0.7963000000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07939999999999914</v>
+        <v>0.2690999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7018</v>
+        <v>0.5271999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3833000000000001</v>
+        <v>-0.3727999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9363999999999999</v>
+        <v>-0.9293999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5532</v>
+        <v>0.5565</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8793</v>
+        <v>1.0016</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3470000000000001</v>
+        <v>0.4306000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5322999999999998</v>
+        <v>0.5710999999999998</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2623</v>
+        <v>-1.3746</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2833</v>
+        <v>-1.36</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02100000000000002</v>
+        <v>-0.01449999999999985</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4097</v>
+        <v>0.4048999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4581</v>
+        <v>2.4295</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01719999999999999</v>
+        <v>-0.005900000000000016</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06809999999999983</v>
+        <v>0.1016000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08540000000000005</v>
+        <v>-0.1075</v>
       </c>
       <c r="V7" t="n">
-        <v>0.772</v>
+        <v>0.7701</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4086</v>
+        <v>-0.4201</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2669999999999999</v>
+        <v>0.1542</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7392</v>
+        <v>-2.4904</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0063</v>
+        <v>2.6446</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.8992</v>
+        <v>-6.934</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4421</v>
+        <v>-2.4695</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.4569</v>
+        <v>-4.4645</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2337</v>
+        <v>-2.0897</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8244</v>
+        <v>1.9129</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.058</v>
+        <v>-4.0025</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.6654</v>
+        <v>-4.8443</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.2665</v>
+        <v>-4.3825</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3990000000000001</v>
+        <v>-0.4619</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2049000000000001</v>
+        <v>0.2023999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.3017</v>
+        <v>-4.2516</v>
       </c>
       <c r="R8" t="n">
-        <v>4.5066</v>
+        <v>4.454</v>
       </c>
       <c r="S8" t="n">
-        <v>7.4276</v>
+        <v>7.348800000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>2.9638</v>
+        <v>3.0045</v>
       </c>
       <c r="U8" t="n">
-        <v>4.4638</v>
+        <v>4.3441</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4662999999999999</v>
+        <v>-0.4632000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8324</v>
+        <v>0.8459999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2987</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09830000000000005</v>
+        <v>-0.3256999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6569</v>
+        <v>-2.473100000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5586</v>
+        <v>2.1475</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9312</v>
+        <v>-4.9762</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4791</v>
+        <v>-2.5466</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4522</v>
+        <v>-2.4298</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7431</v>
+        <v>-2.6142</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2859</v>
+        <v>1.3413</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.029</v>
+        <v>-3.9556</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.188</v>
+        <v>-2.362</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.7649</v>
+        <v>-3.8879</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5768</v>
+        <v>1.5258</v>
       </c>
       <c r="P9" t="n">
-        <v>5.1212</v>
+        <v>5.0613</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5.1212</v>
+        <v>5.0613</v>
       </c>
       <c r="S9" t="n">
-        <v>4.270099999999999</v>
+        <v>4.213900000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08620000000000005</v>
+        <v>0.1411000000000002</v>
       </c>
       <c r="U9" t="n">
-        <v>4.1839</v>
+        <v>4.0729</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.5586</v>
+        <v>-4.6245</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.5586</v>
+        <v>-4.6245</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9509</v>
+        <v>-4.9419</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5815</v>
+        <v>-3.4892</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3695</v>
+        <v>-1.4526</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4215</v>
+        <v>-2.4356</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6162</v>
+        <v>-0.6318</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8053</v>
+        <v>-1.8038</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9238999999999999</v>
+        <v>-0.8868999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4156</v>
+        <v>0.434</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3395</v>
+        <v>-1.3209</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4976</v>
+        <v>-1.5485</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0319</v>
+        <v>-1.0657</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4658</v>
+        <v>-0.4828</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R10" t="n">
-        <v>1.229</v>
+        <v>1.2148</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.07490000000000002</v>
+        <v>-0.06890000000000002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1547</v>
+        <v>-0.1404</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0796</v>
+        <v>0.0713</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.635</v>
+        <v>-1.6276</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4544</v>
+        <v>-0.4374</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.8568</v>
+        <v>-6.9386</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.539899999999999</v>
+        <v>-4.2973</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3168</v>
+        <v>-2.6413</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.447800000000001</v>
+        <v>-9.464400000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.8551</v>
+        <v>-3.8735</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.5926</v>
+        <v>-5.5909</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.4715</v>
+        <v>-4.3582</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6241</v>
+        <v>-1.5646</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.8475</v>
+        <v>-2.7937</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.9761</v>
+        <v>-5.1061</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2311</v>
+        <v>-2.3087</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.745</v>
+        <v>-2.7974</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R11" t="n">
-        <v>3.892</v>
+        <v>3.8467</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04339999999999999</v>
+        <v>0.03139999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8409</v>
+        <v>-1.7844</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8842</v>
+        <v>1.8159</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9087999999999998</v>
+        <v>0.8748</v>
       </c>
       <c r="W11" t="n">
-        <v>4.0259</v>
+        <v>4.0725</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.1171</v>
+        <v>-3.1976</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.7599</v>
+        <v>-11.6034</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.0941</v>
+        <v>-9.6241</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6657</v>
+        <v>-1.9793</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.2066</v>
+        <v>-15.0987</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.963800000000001</v>
+        <v>-5.894200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.242800000000001</v>
+        <v>-9.204699999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-10.1508</v>
+        <v>-9.859400000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5858</v>
+        <v>-1.3935</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.565099999999999</v>
+        <v>-8.4659</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.0557</v>
+        <v>-5.2394</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.378</v>
+        <v>-4.5007</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6777</v>
+        <v>-0.7388</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8192999999999999</v>
+        <v>0.8099000000000003</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5067</v>
+        <v>-4.4539</v>
       </c>
       <c r="R12" t="n">
-        <v>5.326</v>
+        <v>5.2638</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3748</v>
+        <v>-1.3352</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2334</v>
+        <v>-1.1686</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1413</v>
+        <v>-0.1667</v>
       </c>
       <c r="V12" t="n">
-        <v>4.0022</v>
+        <v>4.0209</v>
       </c>
       <c r="W12" t="n">
-        <v>5.7969</v>
+        <v>5.8577</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7948</v>
+        <v>-1.8368</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.239200000000002</v>
+        <v>-3.364900000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>2.904299999999999</v>
+        <v>6.538100000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.143199999999999</v>
+        <v>-9.902800000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-33.25580000000001</v>
+        <v>-33.001</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.1239</v>
+        <v>-12.0615</v>
       </c>
       <c r="I13" t="n">
-        <v>-21.1317</v>
+        <v>-20.9398</v>
       </c>
       <c r="J13" t="n">
-        <v>13.5894</v>
+        <v>15.7557</v>
       </c>
       <c r="K13" t="n">
-        <v>25.38600000000001</v>
+        <v>26.7167</v>
       </c>
       <c r="L13" t="n">
-        <v>-11.7967</v>
+        <v>-10.9608</v>
       </c>
       <c r="M13" t="n">
-        <v>-46.8442</v>
+        <v>-48.7567</v>
       </c>
       <c r="N13" t="n">
-        <v>-37.5097</v>
+        <v>-38.7779</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.3347</v>
+        <v>-9.978999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>8.193699999999998</v>
+        <v>8.098300000000002</v>
       </c>
       <c r="Q13" t="n">
-        <v>-46.0904</v>
+        <v>-45.5521</v>
       </c>
       <c r="R13" t="n">
-        <v>54.28410000000001</v>
+        <v>53.65039999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>28.2396</v>
+        <v>28.0554</v>
       </c>
       <c r="T13" t="n">
-        <v>8.693900000000003</v>
+        <v>9.231400000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5453</v>
+        <v>18.8236</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.417000000000002</v>
+        <v>-6.517399999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>26.7123</v>
+        <v>27.1017</v>
       </c>
       <c r="X13" t="n">
-        <v>-33.1296</v>
+        <v>-33.619</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BIELE ISB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BIELE ISB.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6237</v>
+        <v>7.0885</v>
       </c>
       <c r="E2" t="n">
-        <v>18.3843</v>
+        <v>13.1141</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.7606</v>
+        <v>-6.025700000000001</v>
       </c>
       <c r="G2" t="n">
         <v>7.4195</v>
@@ -610,13 +610,13 @@
         <v>5.8712</v>
       </c>
       <c r="S2" t="n">
-        <v>10.8187</v>
+        <v>5.2835</v>
       </c>
       <c r="T2" t="n">
-        <v>8.5517</v>
+        <v>3.2815</v>
       </c>
       <c r="U2" t="n">
-        <v>2.267</v>
+        <v>2.002</v>
       </c>
       <c r="V2" t="n">
         <v>-5.2097</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.696200000000001</v>
+        <v>5.302700000000002</v>
       </c>
       <c r="E3" t="n">
-        <v>1.007699999999999</v>
+        <v>6.438099999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6884</v>
+        <v>-1.1353</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.3418</v>
+        <v>4.1402</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5223</v>
+        <v>-1.5419</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.819599999999999</v>
+        <v>5.6823</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3784</v>
+        <v>10.4588</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3332</v>
+        <v>2.6215</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04519999999999991</v>
+        <v>7.8374</v>
       </c>
       <c r="M3" t="n">
-        <v>-7.7204</v>
+        <v>-6.3185</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.8555</v>
+        <v>-4.1633</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.865</v>
+        <v>-2.1551</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.6441</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.3251</v>
+        <v>-6.478499999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>6.681</v>
+        <v>5.8712</v>
       </c>
       <c r="S3" t="n">
-        <v>8.1282</v>
+        <v>1.9391</v>
       </c>
       <c r="T3" t="n">
-        <v>4.7277</v>
+        <v>0.2637</v>
       </c>
       <c r="U3" t="n">
-        <v>3.4005</v>
+        <v>1.6752</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5539</v>
+        <v>-0.1692</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2264</v>
+        <v>2.194</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6725</v>
+        <v>-2.3632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.854100000000001</v>
+        <v>4.5865</v>
       </c>
       <c r="E4" t="n">
-        <v>4.194</v>
+        <v>4.8304</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3399</v>
+        <v>-0.2438999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1402</v>
+        <v>-1.21</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5419</v>
+        <v>0.7278999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6823</v>
+        <v>-1.9379</v>
       </c>
       <c r="J4" t="n">
-        <v>10.4588</v>
+        <v>6.1175</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6215</v>
+        <v>6.4716</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8374</v>
+        <v>-0.3541000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.3185</v>
+        <v>-7.327599999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.1633</v>
+        <v>-5.7438</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1551</v>
+        <v>-1.5838</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6074000000000001</v>
+        <v>2.4295</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.478499999999999</v>
+        <v>-5.4662</v>
       </c>
       <c r="R4" t="n">
-        <v>5.8712</v>
+        <v>7.8956</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5097</v>
+        <v>3.5793</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.9803</v>
+        <v>0.7948</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4707000000000001</v>
+        <v>2.7845</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1692</v>
+        <v>-0.2122999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>2.194</v>
+        <v>3.3841</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3632</v>
+        <v>-3.5964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2067</v>
+        <v>2.5674</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1709</v>
+        <v>4.196</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9642000000000002</v>
+        <v>-1.6285</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.21</v>
+        <v>0.2727999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7278999999999999</v>
+        <v>-0.2147000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.9379</v>
+        <v>0.4874999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>6.1175</v>
+        <v>3.2313</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4716</v>
+        <v>2.3495</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3541000000000001</v>
+        <v>0.8819</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.327599999999999</v>
+        <v>-2.9584</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.7438</v>
+        <v>-2.5642</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5838</v>
+        <v>-0.3942999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4295</v>
+        <v>3.0369</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.4662</v>
+        <v>-2.0246</v>
       </c>
       <c r="R5" t="n">
-        <v>7.8956</v>
+        <v>5.061299999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1995999999999999</v>
+        <v>1.6883</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.8645</v>
+        <v>0.9529000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>2.0641</v>
+        <v>0.7355</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2122999999999999</v>
+        <v>-2.4306</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3841</v>
+        <v>2.0362</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.5964</v>
+        <v>-4.4668</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>O. INDA HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1135</v>
+        <v>1.4885</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8862</v>
+        <v>0.3330000000000006</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7726</v>
+        <v>1.1555</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2727999999999999</v>
+        <v>-0.3727999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2147000000000001</v>
+        <v>-0.9293999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4874999999999999</v>
+        <v>0.5565</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2313</v>
+        <v>1.0016</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3495</v>
+        <v>0.4306000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8819</v>
+        <v>0.5710999999999998</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9584</v>
+        <v>-1.3746</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5642</v>
+        <v>-1.36</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3942999999999999</v>
+        <v>-0.01449999999999985</v>
       </c>
       <c r="P6" t="n">
-        <v>3.0369</v>
+        <v>0.4048999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.0246</v>
       </c>
       <c r="R6" t="n">
-        <v>5.061299999999999</v>
+        <v>2.4295</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2345</v>
+        <v>0.6863999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.357</v>
+        <v>0.1656</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5912999999999999</v>
+        <v>0.5206999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4306</v>
+        <v>0.7701</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0362</v>
+        <v>1.1902</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.4668</v>
+        <v>-0.4201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. INDA HERNANDEZ</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7963000000000002</v>
+        <v>-0.2847000000000006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2690999999999997</v>
+        <v>-1.6274</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5271999999999999</v>
+        <v>1.3427</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3727999999999999</v>
+        <v>-4.3418</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9293999999999999</v>
+        <v>-1.5223</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5565</v>
+        <v>-2.819599999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0016</v>
+        <v>3.3784</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4306000000000001</v>
+        <v>3.3332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5710999999999998</v>
+        <v>0.04519999999999991</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3746</v>
+        <v>-7.7204</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.36</v>
+        <v>-4.8555</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.01449999999999985</v>
+        <v>-2.865</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4048999999999999</v>
+        <v>-3.6441</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0246</v>
+        <v>-10.3251</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4295</v>
+        <v>6.681</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.005900000000000016</v>
+        <v>5.1475</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1016000000000001</v>
+        <v>2.0926</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1075</v>
+        <v>3.0547</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7701</v>
+        <v>2.5539</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1902</v>
+        <v>3.2264</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4201</v>
+        <v>-0.6725</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1542</v>
+        <v>-0.4166</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4904</v>
+        <v>-1.7862</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6446</v>
+        <v>1.3695</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.934</v>
+        <v>-4.9762</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4695</v>
+        <v>-2.5466</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.4645</v>
+        <v>-2.4298</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0897</v>
+        <v>-2.6142</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9129</v>
+        <v>1.3413</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.0025</v>
+        <v>-3.9556</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.8443</v>
+        <v>-2.362</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.3825</v>
+        <v>-3.8879</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4619</v>
+        <v>1.5258</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2023999999999999</v>
+        <v>5.0613</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.2516</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.454</v>
+        <v>5.0613</v>
       </c>
       <c r="S8" t="n">
-        <v>7.348800000000001</v>
+        <v>4.123</v>
       </c>
       <c r="T8" t="n">
-        <v>3.0045</v>
+        <v>0.8280000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>4.3441</v>
+        <v>3.2948</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4632000000000001</v>
+        <v>-4.6245</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8459999999999999</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3092</v>
+        <v>-4.6245</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3256999999999999</v>
+        <v>-3.0918</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.473100000000001</v>
+        <v>-4.463</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1475</v>
+        <v>1.3711</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9762</v>
+        <v>-6.934</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5466</v>
+        <v>-2.4695</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4298</v>
+        <v>-4.4645</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6142</v>
+        <v>-2.0897</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3413</v>
+        <v>1.9129</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.9556</v>
+        <v>-4.0025</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.362</v>
+        <v>-4.8443</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.8879</v>
+        <v>-4.3825</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5258</v>
+        <v>-0.4619</v>
       </c>
       <c r="P9" t="n">
-        <v>5.0613</v>
+        <v>0.2023999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.2516</v>
       </c>
       <c r="R9" t="n">
-        <v>5.0613</v>
+        <v>4.454</v>
       </c>
       <c r="S9" t="n">
-        <v>4.213900000000001</v>
+        <v>4.1029</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1411000000000002</v>
+        <v>1.0321</v>
       </c>
       <c r="U9" t="n">
-        <v>4.0729</v>
+        <v>3.0708</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.6245</v>
+        <v>-0.4632000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8459999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.6245</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9419</v>
+        <v>-4.284599999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4892</v>
+        <v>-3.1778</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4526</v>
+        <v>-1.1068</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4356</v>
@@ -1234,13 +1234,13 @@
         <v>1.2148</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06890000000000002</v>
+        <v>0.5883</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1404</v>
+        <v>0.1711</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0713</v>
+        <v>0.4171</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6276</v>
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9386</v>
+        <v>-6.464399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2973</v>
+        <v>-2.9874</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6413</v>
+        <v>-3.477</v>
       </c>
       <c r="G11" t="n">
         <v>-9.464400000000001</v>
@@ -1312,13 +1312,13 @@
         <v>3.8467</v>
       </c>
       <c r="S11" t="n">
-        <v>0.03139999999999998</v>
+        <v>0.5056</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7844</v>
+        <v>-0.4747</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8159</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0.8748</v>
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.6034</v>
+        <v>-8.523800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.6241</v>
+        <v>-7.6914</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9793</v>
+        <v>-0.8323</v>
       </c>
       <c r="G12" t="n">
         <v>-15.0987</v>
@@ -1390,13 +1390,13 @@
         <v>5.2638</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3352</v>
+        <v>1.7443</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1686</v>
+        <v>0.7641000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1667</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>4.0209</v>
@@ -1423,13 +1423,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.364900000000002</v>
+        <v>-2.032299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.538100000000002</v>
+        <v>7.178399999999995</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.902800000000001</v>
+        <v>-9.210700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-33.001</v>
@@ -1459,7 +1459,7 @@
         <v>-9.978999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>8.098300000000002</v>
+        <v>8.0983</v>
       </c>
       <c r="Q13" t="n">
         <v>-45.5521</v>
@@ -1468,13 +1468,13 @@
         <v>53.65039999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>28.0554</v>
+        <v>29.3882</v>
       </c>
       <c r="T13" t="n">
-        <v>9.231400000000002</v>
+        <v>9.871700000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>18.8236</v>
+        <v>19.5159</v>
       </c>
       <c r="V13" t="n">
         <v>-6.517399999999998</v>
